--- a/config/pcs/PCS_英博_125.xlsx
+++ b/config/pcs/PCS_英博_125.xlsx
@@ -2316,7 +2316,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2342,6 +2342,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -2491,7 +2499,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2501,6 +2509,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2830,16 +2844,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2848,37 +2859,37 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2893,74 +2904,77 @@
     <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3000,6 +3014,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -3360,58 +3380,58 @@
     <col min="13" max="13" width="50.0476190476191" style="2" customWidth="1"/>
     <col min="14" max="14" width="60.6190476190476" style="2" customWidth="1"/>
     <col min="15" max="15" width="23.8015873015873" style="2" customWidth="1"/>
-    <col min="16" max="16" width="78.6428571428571" style="5" customWidth="1"/>
+    <col min="16" max="16" width="78.4047619047619" style="5" customWidth="1"/>
     <col min="17" max="32" width="9.11111111111111" style="2"/>
     <col min="33" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:16">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+    <row r="1" s="14" customFormat="1" customHeight="1" spans="1:16">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="P1" s="15" t="s">
         <v>15</v>
       </c>
     </row>
